--- a/セリフ編集/キャラタイプ別/標準×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×感情的.xlsx
@@ -257,7 +257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -315,22 +315,22 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.standard.hit[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard.hit[1]</t>
+          <t xml:space="preserve">atk.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -340,29 +340,29 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで終わったら……また、あの日の景色に戻っちゃう……っ!</t>
+          <t xml:space="preserve">負けたくないっ…！</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.standard.hit[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard.hit[2]</t>
+          <t xml:space="preserve">atk.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -372,29 +372,29 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">立つ……立たなきゃ……あそこに切られた、あの日の私のために……!</t>
+          <t xml:space="preserve">絶対に…絶対にっ…！</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.standard.win[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard.win[1]</t>
+          <t xml:space="preserve">atk.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -404,29 +404,29 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの日、リングを降ろされた私が……今、あそこの選手に勝った……っ!</t>
+          <t xml:space="preserve">うぅっ…でも、負けないっ…！</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.standard.win[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.emotional[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard.win[2]</t>
+          <t xml:space="preserve">atk.standard.emotional[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -436,1132 +436,4236 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てた……? 切られても、私、ちゃんと戦ってるよ……!</t>
+          <t xml:space="preserve">こんなところで…終われないっ！</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.lose[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.lose[1]</t>
+          <t xml:space="preserve">bigmove.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました……。ごめんなさい、悔しいです。</t>
+          <t xml:space="preserve">うぅっ…絶対に…決めるんだ…！</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.lose[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.lose[2]</t>
+          <t xml:space="preserve">bigmove.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くやしい……! ごめんなさい、涙が止まらなくて。</t>
+          <t xml:space="preserve">泣かない…泣かないから…いくよ！</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.lose[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.lose[3]</t>
+          <t xml:space="preserve">bigmove.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てなかった……。あんなに、お願いしたのに。</t>
+          <t xml:space="preserve">ここで…ここでっ…！</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.petition[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.petition[1]</t>
+          <t xml:space="preserve">climax.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長! あの人とやりたいんです、お願いします!</t>
+          <t xml:space="preserve">（胸が苦しい…でも、この痛みが、生きてる証だから）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.petition[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.petition[2]</t>
+          <t xml:space="preserve">climax.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう我慢できないんです。あの人と、やらせてください。</t>
+          <t xml:space="preserve">（お願い、身体…もう少しだけ動いて）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.petition[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.petition[3]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと考えてました。……お願いします、どうしても!</t>
+          <t xml:space="preserve">痛いっ…！ でも…でもっ…！</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.sendoff[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.sendoff[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます! 絶対、勝ってきます!</t>
+          <t xml:space="preserve">うぅっ…こんなので…負けないっ…！</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.sendoff[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.sendoff[2]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うれしい……ありがとうございます。行ってきます!</t>
+          <t xml:space="preserve">泣かない…泣かないよ…まだ…！</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.sendoff[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.emotional.hit[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.sendoff[3]</t>
+          <t xml:space="preserve">standard.emotional.hit[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">泣きそうです。……ありがとうございます!</t>
+          <t xml:space="preserve">ここで終わったら……また、あの日の景色に戻っちゃう……っ!</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.emotional.hit[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.win[1]</t>
+          <t xml:space="preserve">standard.emotional.hit[2]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました! 社長、勝ちましたよ!</t>
+          <t xml:space="preserve">立つ……立たなきゃ……あそこに切られた、あの日の私のために……!</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.emotional.win[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.win[2]</t>
+          <t xml:space="preserve">standard.emotional.win[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった……! 見ててくれましたか!</t>
+          <t xml:space="preserve">あの日、リングを降ろされた私が……今、あそこの選手に勝った……っ!</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.win[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.emotional.win[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.win[3]</t>
+          <t xml:space="preserve">standard.emotional.win[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた……。うれしくて、声が震えてます。</t>
+          <t xml:space="preserve">見てた……? 切られても、私、ちゃんと戦ってるよ……!</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional._accept[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional._accept[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等! そっちが名前を出したんだからね!</t>
+          <t xml:space="preserve">嘘…動けないっ</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional._accept[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional._accept[2]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだんだ。……絶対、後悔させてやる。</t>
+          <t xml:space="preserve">間に合わないっ…！</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional._accept[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional._accept[3]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言ったな? もう引っ込みつかないよ、お互い!</t>
+          <t xml:space="preserve">ごめん…ごめんっ…！</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.draw[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.draw[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかずって何!? 中途半端すぎるでしょ!</t>
+          <t xml:space="preserve">絶対させないっ…！</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.draw[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.draw[2]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わってない! こんなので終わらせない!</t>
+          <t xml:space="preserve">まだっ…！</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.draw[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.draw[3]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一回! いますぐもう一回やろうよ!</t>
+          <t xml:space="preserve">そんなの…駄目っ…！</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.lose[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.lose[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそ……! 認めない、絶対に認めないから!</t>
+          <t xml:space="preserve">二人でっ…！</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.lose[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.lose[2]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた……。悔しい、悔しいよ……!</t>
+          <t xml:space="preserve">合わせるよ…っ！</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.lose[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.lose[3]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで……! こんなの、納得できるわけない!</t>
+          <t xml:space="preserve">絶対決めるっ…！</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.win[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.win[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほら見なさい! わたしを選んだのが間違い!</t>
+          <t xml:space="preserve">絶対…勝つ…！</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.win[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.win[2]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……! ざまあみろって、言っていい?</t>
+          <t xml:space="preserve">お疲れ…ここからは私が…！</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.win[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_emotional.win[3]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで分かったでしょ! 二度と名前呼ばないで!</t>
+          <t xml:space="preserve">任せて…絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.emotional.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嫌だ……あの子たちと同じ方向は向けない……！</t>
+          <t xml:space="preserve">{partner}っ…ごめんっ…ごめんねっ…！</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.emotional.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うそ……うそだよ……あの人が……！</t>
+          <t xml:space="preserve">次は絶対…絶対勝つからっ…！ {partner}…！</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.emotional.standard[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard[2]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたし、どうすれば……あたし、あの人のために頑張ってたのに……！</t>
+          <t xml:space="preserve">{partner}っ…！ ありがとう…二人で、勝ったよ…！</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.emotional.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">だってあの子たちの前だと……素でいられるんだもん！</t>
+          <t xml:space="preserve">絶対勝つって、約束したもんね…{partner}…っ！</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.emotional.standard[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.lose[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard[2]</t>
+          <t xml:space="preserve">standard_emotional.lose[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい、ごめんなさい……でも、止められない……！</t>
+          <t xml:space="preserve">負けました……。ごめんなさい、悔しいです。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.emotional.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.lose[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard[1]</t>
+          <t xml:space="preserve">standard_emotional.lose[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長！　あたしの子たちが、どんな思いしてるか、わかってます？</t>
+          <t xml:space="preserve">くやしい……! ごめんなさい、涙が止まらなくて。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.emotional.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.lose[3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard.high[1]</t>
+          <t xml:space="preserve">standard_emotional.lose[3]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな、ありがとう……ありがとう</t>
+          <t xml:space="preserve">勝てなかった……。あんなに、お願いしたのに。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.emotional.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.petition[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard.high[1]</t>
+          <t xml:space="preserve">standard_emotional.petition[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな、見ててね</t>
+          <t xml:space="preserve">社長! あの人とやりたいんです、お願いします!</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.emotional.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.petition[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard.high[1]</t>
+          <t xml:space="preserve">standard_emotional.petition[2]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしたち、今日で全部背負って戦います</t>
+          <t xml:space="preserve">もう我慢できないんです。あの人と、やらせてください。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.emotional.standard.high[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.petition[3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.standard.high[2]</t>
+          <t xml:space="preserve">standard_emotional.petition[3]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの組の名前、今夜傷つけさせない</t>
+          <t xml:space="preserve">ずっと考えてました。……お願いします、どうしても!</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.emotional.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.sendoff[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.sendoff[1]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます! 絶対、勝ってきます!</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うれしい……ありがとうございます。行ってきます!</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">泣きそうです。……ありがとうございます!</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.win[1]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.win[1]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました! 社長、勝ちましたよ!</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.win[2]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.win[2]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やった……! 見ててくれましたか!</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_emotional.win[3]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.win[3]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てた……。うれしくて、声が震えてます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional._accept[1]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional._accept[1]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">上等! そっちが名前を出したんだからね!</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional._accept[2]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional._accept[2]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしを選んだんだ。……絶対、後悔させてやる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional._accept[3]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional._accept[3]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">言ったな? もう引っ込みつかないよ、お互い!</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.draw[1]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.draw[1]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着つかずって何!? 中途半端すぎるでしょ!</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.draw[2]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.draw[2]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わってない! こんなので終わらせない!</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.draw[3]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.draw[3]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう一回! いますぐもう一回やろうよ!</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.lose[1]</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.lose[1]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">くっそ……! 認めない、絶対に認めないから!</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.lose[2]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.lose[2]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けた……。悔しい、悔しいよ……!</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.lose[3]</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.lose[3]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">なんで……! こんなの、納得できるわけない!</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.win[1]</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.win[1]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ほら見なさい! わたしを選んだのが間違い!</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.win[2]</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.win[2]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った……! ざまあみろって、言っていい?</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_emotional.win[3]</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_emotional.win[3]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これで分かったでしょ! 二度と名前呼ばないで!</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、頼みます。私たちのメンバー、もっと大切に扱ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、頼みます。メイン、私たちに回してください。今の私たちなら必ず応えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、お願いします。私たちのメンバー、もっと正当に評価されてもいいはずです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、私たちのメンバーがやってきたこと、ちゃんと見てください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます…社長、その一言、ずっと欲しかったです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ああ、社長…そういう答え方、ですか。…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長…ありがとうございます。応えてみせます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですか。次の機会に、また。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですね。社長の判断、信じます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。社長…これ、忘れません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですか。…わかりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…そういう形ですか。…わかりました、ありがたいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます…社長、その言葉、染みます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…そういう答え方、好きです。ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ああ、…そう、ですか。…悪いことしました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないですね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですね、悪かったです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…私、止まれないですから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、すみません。…言い訳できないです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます…社長、優しい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…私の穴、埋めてくれるんですか。…申し訳ないです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…見ててくれたんですね。…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…大丈夫です。…まだ、やれます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…ありがとうございます。一人で抱えなくていいって、思えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そう、ですか。…私の至らなさです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…そういう形で気にかけてくれるの、ありがたいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですね、悪かったです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（…目元に力が入ったが、言葉は出てこなかった）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですね。すみません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…そう、ですか。…私が、追い込みすぎてました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。やり切らせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…ありがとうございます。私、見えてなかったです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.standard</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.attack.standard</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">許せない、あの子のやり方</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.standard</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.defend.standard</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こっちだって、引けないの</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr" s="2">
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あたし、あの人のこと信じてたのに……ひどい！</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう、無理だよ……泣きたい……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっと、気まずかったの……嬉しい……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう、我慢できない！　あの子とは、決着をつける！</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.emotional.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悔しい……ぜんぜん、納得いかない……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.emotional.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめん、みんな……次は、絶対勝つから……</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.emotional.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（嗚咽だけが漏れる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.emotional.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うっ……うぅ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った！　うちのみんなのために、勝った！</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんたら、もう泣かせないからね、絶対！</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.emotional.low[1]</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.low[1]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った……</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.emotional.mid[1]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.mid[1]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てた……みんな、ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう、我慢できない！　あんたんとこの組、今夜で終わりにする！</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うちのみんなが泣いた分、ぜんぶ返してもらうから</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.emotional.low[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.low[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう、泣いてる暇なんか、ない</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.emotional.mid[1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.mid[1]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日のあたし、止めても無駄だよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんたが本気なら、あたしも本気で受ける！</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うちの子たちのこと、もう傷つけさせない！</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.emotional.low[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.low[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……分かった。ぶつかろう</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.emotional.mid[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.mid[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受ける。今日は引かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うちの組、今夜は弱かった。みんな、ごめん</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんな、ありがとう……ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめん、ごめんね</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんな、見ててね</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">背負ってるもの、見せます</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしたち、今日で全部背負って戦います</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うちの組の名前、今夜傷つけさせない</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">emotional.standard.high[1]</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr" s="3">
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたしたちも、今夜は退きません</t>
         </is>
       </c>
     </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.emotional.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんね、みんな。守れなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.emotional.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめん</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.emotional.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うちの背中、もう、頼りにならないかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った……勝っちゃった……</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">怖いよ。でも、行かなきゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[2]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ごめん、ごめんね……それでも、譲れないんだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional.high[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">そんな顔で来られたら――退けないじゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来た…! 身体は痛いけど、最後まで絶対立ってやる…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あと一つ…! 繋いでくれた分、私が締める…! 泣くのは後だ…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">来い…! 目の前の一人から、全部倒して繋いでやる…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">止まりたくない…! この一戦から、全力でいく…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人倒した…! はぁ…まだ立ってる…! 次、来い…! ここは渡さねえ…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ終わらない…! この勢いのまま、次も倒す…! 出てこい…!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H40"/>
+  <autoFilter ref="A1:H137"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×感情的.xlsx
@@ -257,7 +257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H462"/>
+  <dimension ref="A1:H464"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で戦い続けるのは寂しかったから…仲��ができるのが嬉しいです…！</t>
+          <t xml:space="preserve">一人で戦い続けるのは寂しかったから…仲間ができるのが嬉しいです…！</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったって言っただろ……！ なんでまだ、いるんだ</t>
+          <t xml:space="preserve">終わったって言ったのに……！ なんで、まだいるの</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わってない……！ 勝手に終わらせるな……！</t>
+          <t xml:space="preserve">終わってない……！ 勝手に終わらせないで……！</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等! そっちが名前を出したんだからね!</t>
+          <t xml:space="preserve">いいよ、受ける！ そっちが名前を出したんだからね！</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだんだ。……絶対、後悔させてやる。</t>
+          <t xml:space="preserve">私を選んだんだ。……絶対、後悔させてやる。</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言ったな? もう引っ込みつかないよ、お互い!</t>
+          <t xml:space="preserve">言ったよね？ もう引っ込みつかないよ、お互い！</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそ……! 認めない、絶対に認めないから!</t>
+          <t xml:space="preserve">悔しい……！ 認めない、絶対に認めないから！</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほら見なさい! わたしを選んだのが間違い!</t>
+          <t xml:space="preserve">ほら見なさい！ 私を選んだのが間違い！</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、バカ…泣くんじゃないわよ…あたしまで…っ！</t>
+          <t xml:space="preserve">…っ、バカ…泣くんじゃないわよ…私まで…っ！</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ああ、社長…そういう答え方、ですか。…ありがとうございます。</t>
+          <t xml:space="preserve">…ああ、社長…そういう、答え方…ですか。…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…わかりました、ありがたいです。</t>
+          <t xml:space="preserve">…社長…そういう、形ですか。…わかりました、わかりましたから。</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう答え方、好きです。ありがとうございます。</t>
+          <t xml:space="preserve">…社長…そういう答え方、うれしい…！ …ありがとう、ございます！</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたし、あの人のこと信じてたのに……ひどい！</t>
+          <t xml:space="preserve">私、あの人のこと信じてたのに……ひどい！</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたら、もう泣かせないからね、絶対！</t>
+          <t xml:space="preserve">あなたたち、もう泣かせないからね、絶対！</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、我慢できない！　あんたんとこの組、今夜で終わりにする！</t>
+          <t xml:space="preserve">もう、我慢できない！　あなたの組、今夜で終わりにする！</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のあたし、止めても無駄だよ</t>
+          <t xml:space="preserve">今日の私、止めても無駄だよ</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたが本気なら、あたしも本気で受ける！</t>
+          <t xml:space="preserve">あなたが本気なら、私も本気で受ける！</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受ける。今日は引かない</t>
+          <t xml:space="preserve">受ける…。今日は、今日は引かない…！</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしたち、今日で全部背負って戦います</t>
+          <t xml:space="preserve">私たち、今日で全部背負って戦います</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしたちも、今夜は退きません</t>
+          <t xml:space="preserve">私たちも、今夜は退きません</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…わたしの体、こんなに動けたんだ——！）</t>
+          <t xml:space="preserve">（…私の体、こんなに動けたんだ——！）</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が軽い…!今ならなんでもできる気がする…!</t>
+          <t xml:space="preserve">体が軽い…！今ならなんでもできる気がする…！</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重い…!やる気はあるのに、体がついてこない…!</t>
+          <t xml:space="preserve">体が重い…！やる気はあるのに、体がついてこない…！</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ…なんか入ってこない…!?もっとやれるはずなのに</t>
+          <t xml:space="preserve">あれ…なんか入ってこない…！？もっとやれるはずなのに</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんで泣いてるんだろ、あたし…</t>
+          <t xml:space="preserve">…なんで泣いてるんだろ、私…</t>
         </is>
       </c>
     </row>
@@ -8128,7 +8128,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8153,14 +8153,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合のこと思い出すだけで…っ。ごめんなさい、涙が…最高でした…！</t>
+          <t xml:space="preserve">みんなの声が背中を押してくれました。絶対に忘れません。</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[1]</t>
+          <t xml:space="preserve">bestMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8185,14 +8185,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトに…どれだけの想いが詰まってるか…っ。絶対、手放さない…！</t>
+          <t xml:space="preserve">あの試合のこと思い出すだけで…っ。ごめんなさい、涙が…最高でした…！</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.emotional[1]</t>
+          <t xml:space="preserve">champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">プロレスが…わたしの居場所だった…。ここで出会えた人たちが…全部…宝物で…っ！</t>
+          <t xml:space="preserve">このベルトに…どれだけの想いが詰まってるか…っ。絶対、手放さない…！</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.emotional[1]</t>
+          <t xml:space="preserve">hallOfFame.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間…苦しくて…でも…全部やってきてよかった…っ！ ありがとう…！</t>
+          <t xml:space="preserve">プロレスが…私の居場所だった…。ここで出会えた人たちが…全部…宝物で…っ！</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.emotional[1]</t>
+          <t xml:space="preserve">mvp.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ…だめだ、泣いちゃう…。嬉しいです…こんなに…嬉しいの初めてです…！</t>
+          <t xml:space="preserve">一年間…苦しくて…でも…全部やってきてよかった…っ！ ありがとう…！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">rookie.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームまで来たんですね、私たち</t>
+          <t xml:space="preserve">あ…だめだ、泣いちゃう…。嬉しいです…こんなに…嬉しいの初めてです…！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">springTagChampion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8345,14 +8345,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">胸がいっぱいで…うまく言葉が出ません</t>
+          <t xml:space="preserve">相棒と抱き合った瞬間、ここまでの全部が報われた気がしました。</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.emotional[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[3]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に、絶対に良い試合にします!</t>
+          <t xml:space="preserve">…ドームまで来たんですね、私たち</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8409,14 +8409,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員って…満員って言いました? …涙が止まりません…!</t>
+          <t xml:space="preserve">胸がいっぱいで…うまく言葉が出ません</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…本当に…本当にありがとうございます…!</t>
+          <t xml:space="preserve">絶対に、絶対に良い試合にします！</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.emotional[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[3]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8473,14 +8473,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この日のこと、絶対に、絶対に忘れません!</t>
+          <t xml:space="preserve">満員って…満員って言いました？ …涙が止まりません…！</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.emotional[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわあ…！練習が楽しい…！もっとやりたい！</t>
+          <t xml:space="preserve">社長…本当に…本当にありがとうございます…！</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.emotional[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8522,29 +8522,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が動くようになってきた…嬉しい…！</t>
+          <t xml:space="preserve">この日のこと、絶対に、絶対に忘れません！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.emotional[1]</t>
+          <t xml:space="preserve">N1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのこと大好き…！一緒にいられて幸せ…！</t>
+          <t xml:space="preserve">うわあ…！練習が楽しい…！もっとやりたい！</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.emotional[1]</t>
+          <t xml:space="preserve">N1.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うう…体がしんどい…でも、でも頑張りたいのに…！</t>
+          <t xml:space="preserve">体が動くようになってきた…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.emotional[1]</t>
+          <t xml:space="preserve">N2.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8633,14 +8633,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなが応援してくれてる…！嬉しくて泣きそう…！</t>
+          <t xml:space="preserve">みんなのこと大好き…！一緒にいられて幸せ…！</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.emotional[1]</t>
+          <t xml:space="preserve">N3.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…もう分かんない…！どうすればいいの…！</t>
+          <t xml:space="preserve">うう…体がしんどい…でも、でも頑張りたいのに…！</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.emotional[1]</t>
+          <t xml:space="preserve">N4.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんか、最近ずっとモヤモヤして…うまく言えないけど…</t>
+          <t xml:space="preserve">みんなが応援してくれてる…！嬉しくて泣きそう…！</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">N5_low.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うれしい…ここにいてよかった</t>
+          <t xml:space="preserve">もう…もう分かんない…！どうすればいいの…！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">N5_warning.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんで…なんでだろ</t>
+          <t xml:space="preserve">…なんか、最近ずっとモヤモヤして…うまく言えないけど…</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">breakthrough.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいな</t>
+          <t xml:space="preserve">…うれしい…ここにいてよかった</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">G1.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…先に始めたのはあたしなのに</t>
+          <t xml:space="preserve">…なんで…なんでだろ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">G1.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8857,14 +8857,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…置いていかれてる気がする</t>
+          <t xml:space="preserve">…悔しいな</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">G2.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8889,14 +8889,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しくないって言ったら嘘になる</t>
+          <t xml:space="preserve">…先に始めたのは私なのに</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">G2.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8921,14 +8921,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたしも、あそこに立ちたい</t>
+          <t xml:space="preserve">…置いていかれてる気がする</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">G3.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてるのかな、あたしのこと</t>
+          <t xml:space="preserve">…悔しくないって言ったら嘘になる</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">G3.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんな、あたしのこと嫌いなのかな</t>
+          <t xml:space="preserve">…私も、あそこに立ちたい</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">G4.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9017,14 +9017,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいていいのかな</t>
+          <t xml:space="preserve">…見てくれてるのかな、私のこと</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.standard.emotional[1]</t>
+          <t xml:space="preserve">R2.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9049,14 +9049,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やだ。嫌だよ。なんで…</t>
+          <t xml:space="preserve">…みんな、私のこと嫌いなのかな</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.standard.emotional[2]</t>
+          <t xml:space="preserve">R2.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9081,14 +9081,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{name2}がいないなんて、あたし…</t>
+          <t xml:space="preserve">…ここにいていいのかな</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">R3.modal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9113,14 +9113,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った…勝ったよ…！</t>
+          <t xml:space="preserve">…やだ。嫌だよ。なんで…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">R3.modal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…泣くな、あたし。まだ先がある</t>
+          <t xml:space="preserve">…{name2}がいないなんて、私…</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">R4.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい…悔しい…！</t>
+          <t xml:space="preserve">…勝った…勝ったよ…！</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.standard.emotional[2]</t>
+          <t xml:space="preserve">R4.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9209,14 +9209,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんであたしは勝てないの</t>
+          <t xml:space="preserve">…泣くな、私。まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.standard.emotional[1]</t>
+          <t xml:space="preserve">R5.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9241,14 +9241,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った…！ みんなのおかげだよ…！</t>
+          <t xml:space="preserve">…悔しい…悔しい…！</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9258,29 +9258,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.emotional[1]</t>
+          <t xml:space="preserve">R5.voice.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え……これだけ、ですか……私って、その程度なんだ……</t>
+          <t xml:space="preserve">…なんで私は勝てないの</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9290,29 +9290,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.emotional[1]</t>
+          <t xml:space="preserve">warVictory.voice.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また…？（少し困った顔をしている）</t>
+          <t xml:space="preserve">…勝った…！ みんなのおかげだよ…！</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.emotional[1]</t>
+          <t xml:space="preserve">bonus_insult.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9337,14 +9337,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…！ありがとうございます…！嬉しい…！</t>
+          <t xml:space="preserve">え……これだけ、ですか……私って、その程度なんだ……</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.emotional[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.emotional[2]</t>
+          <t xml:space="preserve">bonus_repeat.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9369,14 +9369,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわあ…嬉しくて泣きそう…！</t>
+          <t xml:space="preserve">…また…？（少し困った顔をしている）</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.emotional[1]</t>
+          <t xml:space="preserve">bonus.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9401,14 +9401,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿…！みんなで強くなれる…！最高だよ…！</t>
+          <t xml:space="preserve">え…！ありがとうございます…！嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.emotional[1]</t>
+          <t xml:space="preserve">bonus.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9433,14 +9433,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ！ずっと見てくれてたんですね…！泣いちゃう…でも頑張る…！</t>
+          <t xml:space="preserve">うわあ…嬉しくて泣きそう…！</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.emotional[1]</t>
+          <t xml:space="preserve">camp.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9465,14 +9465,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ！ありがとうございます…！もう一回…もう一回頑張ります…！</t>
+          <t xml:space="preserve">合宿…！みんなで強くなれる…！最高だよ…！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.emotional[1]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9497,14 +9497,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして…！ わたし、何か間違えましたか…！</t>
+          <t xml:space="preserve">…っ！ずっと見てくれてたんですね…！泣いちゃう…でも頑張る…！</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.emotional[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.emotional[2]</t>
+          <t xml:space="preserve">encourage.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9529,14 +9529,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな、わたしを信じてついてきてくれたのに…</t>
+          <t xml:space="preserve">…っ！ありがとうございます…！もう一回…もう一回頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.emotional[1]</t>
+          <t xml:space="preserve">faction_decree.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9561,14 +9561,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ…！？ うわあ…緊張するけど嬉しい…！頑張る…！</t>
+          <t xml:space="preserve">どうして…！ 私、何か間違えましたか…！</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.emotional[1]</t>
+          <t xml:space="preserve">faction_decree.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9593,14 +9593,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな〜！楽しい〜！大好き〜！</t>
+          <t xml:space="preserve">みんな、私を信じてついてきてくれたのに…</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.emotional[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.emotional[2]</t>
+          <t xml:space="preserve">media.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9625,14 +9625,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう時間…最高だよ…！</t>
+          <t xml:space="preserve">テレビ…！？ うわあ…緊張するけど嬉しい…！頑張る…！</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.emotional[1]</t>
+          <t xml:space="preserve">party.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9657,14 +9657,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">休んでいいんですか…？ ありがとうございます…リフレッシュしてきます…！</t>
+          <t xml:space="preserve">みんな〜！楽しい〜！大好き〜！</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.emotional[1]</t>
+          <t xml:space="preserve">party.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9689,14 +9689,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、こんなにしてもらって…っ、絶対早く戻ります…！</t>
+          <t xml:space="preserve">こういう時間…最高だよ…！</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.emotional[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9721,14 +9721,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ええっ…！専属トレーナー…！頑張ります…！嬉しい…！</t>
+          <t xml:space="preserve">休んでいいんですか…？ ありがとうございます…リフレッシュしてきます…！</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.emotional[1]</t>
+          <t xml:space="preserve">special_treatment.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9753,14 +9753,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ…！？ えっ…嬉しい…！頑張ります…！</t>
+          <t xml:space="preserve">…っ、こんなにしてもらって…っ、絶対早く戻ります…！</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.emotional[1]</t>
+          <t xml:space="preserve">trainer.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9785,14 +9785,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他の団体からオファーが…どうしよう…迷ってる…</t>
+          <t xml:space="preserve">ええっ…！専属トレーナー…！頑張ります…！嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.emotional[1]</t>
+          <t xml:space="preserve">E1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9817,14 +9817,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理…練習なんてできない…</t>
+          <t xml:space="preserve">テレビ…！？ えっ…嬉しい…！頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.emotional[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.emotional[2]</t>
+          <t xml:space="preserve">E6.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9849,14 +9849,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出してもらえないのに練習して…何になるの…</t>
+          <t xml:space="preserve">他の団体からオファーが…どうしよう…迷ってる…</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.standard.emotional[1]</t>
+          <t xml:space="preserve">S_boycott.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9881,14 +9881,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（涙ぐみながら「もう限界かも…」とチームメイトに打ち明けている）</t>
+          <t xml:space="preserve">もう無理…練習なんてできない…</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.standard.emotional[1]</t>
+          <t xml:space="preserve">S_boycott.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9913,14 +9913,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに涙の絵文字と「もうダメかもしれない」と投稿。炎上し始めている）</t>
+          <t xml:space="preserve">出してもらえないのに練習して…何になるの…</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.emotional[1]</t>
+          <t xml:space="preserve">S_grumble.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9945,14 +9945,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いします…！タイトルマッチに挑ませてください…！</t>
+          <t xml:space="preserve">（涙ぐみながら「もう限界かも…」とチームメイトに打ち明けている）</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.emotional[1]</t>
+          <t xml:space="preserve">S_sns.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9977,14 +9977,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と戦いたい…！お願いします…組んでください…！</t>
+          <t xml:space="preserve">（SNSに涙の絵文字と「もうダメかもしれない」と投稿。炎上し始めている）</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.emotional[1]</t>
+          <t xml:space="preserve">S1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10009,14 +10009,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…体がもう…休ませてください…！</t>
+          <t xml:space="preserve">お願いします…！タイトルマッチに挑ませてください…！</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.emotional[1]</t>
+          <t xml:space="preserve">S2.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10041,14 +10041,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…無理です…！このままだと…私…！</t>
+          <t xml:space="preserve">あの人と戦いたい…！お願いします…組んでください…！</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.emotional[1]</t>
+          <t xml:space="preserve">S3.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10073,14 +10073,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ（泣くのを堪えるように唇を噛んでいる）</t>
+          <t xml:space="preserve">ごめんなさい…体がもう…休ませてください…！</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.emotional[1]</t>
+          <t xml:space="preserve">S4_direct.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10105,14 +10105,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いします…！特訓させてください…！もっと、もっと強くなりたい…！</t>
+          <t xml:space="preserve">…もう…無理です…！このままだと…私…！</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.emotional[1]</t>
+          <t xml:space="preserve">S4_silent.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10137,14 +10137,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の子たちに…私にできることがあるなら…やらせてください！</t>
+          <t xml:space="preserve">……っ（泣くのを堪えるように唇を噛んでいる）</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10154,12 +10154,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.emotional[1]</t>
+          <t xml:space="preserve">S5.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10169,14 +10169,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほんとに……!? 嬉しい……っ……頑張ります……!</t>
+          <t xml:space="preserve">お願いします…！特訓させてください…！もっと、もっと強くなりたい…！</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.emotional[1]</t>
+          <t xml:space="preserve">S6.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10201,14 +10201,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ、わたしに……!? う、嬉しい……!</t>
+          <t xml:space="preserve">後輩の子たちに…私にできることがあるなら…やらせてください！</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.emotional[1]</t>
+          <t xml:space="preserve">E1.accept.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10233,14 +10233,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…！早く治します…早く戻りたい…！</t>
+          <t xml:space="preserve">ほんとに……！？ 嬉しい……っ……頑張ります……！</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.emotional[1]</t>
+          <t xml:space="preserve">E1.recommend.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10265,14 +10265,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理…！あの人と一緒にいると…辛い…！</t>
+          <t xml:space="preserve">えっ、私に……！？ う、嬉しい……！</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.emotional[1]</t>
+          <t xml:space="preserve">B1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10297,14 +10297,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私だって…！私だって辛いのに…！</t>
+          <t xml:space="preserve">ごめんなさい…！早く治します…早く戻りたい…！</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10329,14 +10329,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっブランドコラボ！？ すごい！どんな商品になるの！？</t>
+          <t xml:space="preserve">もう無理…！あの人と一緒にいると…辛い…！</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10361,14 +10361,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMに出るの…！？ うわあああ緊張する！でもやる！</t>
+          <t xml:space="preserve">私だって…！私だって辛いのに…！</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.emotional[1]</t>
+          <t xml:space="preserve">B4_brand.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10393,14 +10393,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会える！！ 絶対みんなを笑顔にしてみせる！！</t>
+          <t xml:space="preserve">えっブランドコラボ！？ すごい！どんな商品になるの！？</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.emotional[1]</t>
+          <t xml:space="preserve">B4_cm.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10425,14 +10425,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ歩くの！？ わあああどうしよう緊張するやつだ！</t>
+          <t xml:space="preserve">CMに出るの…！？ うわあああ緊張する！でもやる！</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.emotional[1]</t>
+          <t xml:space="preserve">B4_fan.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10457,14 +10457,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア！？ えっ、私ほんとに！？ うわ〜〜！</t>
+          <t xml:space="preserve">ファンに会える！！ 絶対みんなを笑顔にしてみせる！！</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.emotional[1]</t>
+          <t xml:space="preserve">B4_fashion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10489,14 +10489,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティ出る！？ テンション上がってきた〜！！</t>
+          <t xml:space="preserve">ランウェイ歩くの！？ わあああどうしよう緊張するやつだ！</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.emotional[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10521,14 +10521,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ…テレビ…！？ 私が…！？ 頑張ります…！頑張ります…！</t>
+          <t xml:space="preserve">グラビア！？ えっ、私ほんとに！？ うわ〜〜！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10538,29 +10538,29 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">B4_variety.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれたら…全力で…全力で頑張ります…！</t>
+          <t xml:space="preserve">バラエティ出る！？ テンション上がってきた〜！！</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10570,29 +10570,29 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">B4.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…この日を、ずっと夢見ていました…！</t>
+          <t xml:space="preserve">えっ…テレビ…！？ 私が…！？ 頑張ります…！頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10602,12 +10602,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10617,14 +10617,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しいです…！ 頑張ります…！ 絶対に…！</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力で頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.emotional[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[3]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10649,14 +10649,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと…ずっと待ってました…！ 全力で、頑張ります…！</t>
+          <t xml:space="preserve">うぅっ…この日を、ずっと夢見ていました…！</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10681,14 +10681,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…！嬉しい…！全力で頑張ります…！</t>
+          <t xml:space="preserve">嬉しいです…！ 頑張ります…！ 絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10713,14 +10713,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…！よろしくお願いします…！頑張ります…！</t>
+          <t xml:space="preserve">ずっと…ずっと待ってました…！ 全力で、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
@@ -10745,14 +10745,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くぅっ…痛い…！ でも、絶対戻ります…！</t>
+          <t xml:space="preserve">ありがとうございます…！嬉しい…！全力で頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10777,14 +10777,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅ…こんなの悔しい…！</t>
+          <t xml:space="preserve">嬉しい…！よろしくお願いします…！頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.emotional[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[3]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10809,14 +10809,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…！ 絶対に、絶対に戻る…！</t>
+          <t xml:space="preserve">くぅっ…痛い…！ でも、絶対戻ります…！</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10841,14 +10841,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったって言っただろ……！ なんでまだ、いるんだ</t>
+          <t xml:space="preserve">うぅ…こんなの悔しい…！</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10858,12 +10858,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10873,14 +10873,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わってない……！ 勝手に終わらせるな……！</t>
+          <t xml:space="preserve">悔しい…！ 絶対に、絶対に戻る…！</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10905,14 +10905,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれたら…全力で…全力で頑張ります…！</t>
+          <t xml:space="preserve">終わったって言ったのに……！ なんで、まだいるの</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10937,14 +10937,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…この日を、ずっと夢見ていました…！</t>
+          <t xml:space="preserve">終わってない……！ 勝手に終わらせないで……！</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.emotional[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.emotional[2]</t>
+          <t xml:space="preserve">draftInterest.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10969,14 +10969,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しいです…！ 頑張ります…！ 絶対に…！</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力で頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.emotional[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.emotional[3]</t>
+          <t xml:space="preserve">draftJoin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11001,14 +11001,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと…ずっと待ってました…！ 全力で、頑張ります…！</t>
+          <t xml:space="preserve">うぅっ…この日を、ずっと夢見ていました…！</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.emotional[1]</t>
+          <t xml:space="preserve">draftJoin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11033,14 +11033,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
+          <t xml:space="preserve">嬉しいです…！ 頑張ります…！ 絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.emotional[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.emotional[2]</t>
+          <t xml:space="preserve">draftJoin.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11065,14 +11065,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれた…！この恩、絶対に返す…！</t>
+          <t xml:space="preserve">ずっと…ずっと待ってました…！ 全力で、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.emotional[1]</t>
+          <t xml:space="preserve">faGreeting.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11097,14 +11097,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…！嬉しい…！全力で頑張ります…！</t>
+          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.emotional[1]</t>
+          <t xml:space="preserve">faGreeting.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11129,14 +11129,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…！よろしくお願いします…！頑張ります…！</t>
+          <t xml:space="preserve">呼んでくれた…！ この恩、絶対に返す…！</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.emotional[1]</t>
+          <t xml:space="preserve">faSigning.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11161,14 +11161,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が軽い…!今ならなんでもできる気がする…!</t>
+          <t xml:space="preserve">ありがとうございます…！嬉しい…！全力で頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.emotional[1]</t>
+          <t xml:space="preserve">faWelcome.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11193,14 +11193,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重い…!やる気はあるのに、体がついてこない…!</t>
+          <t xml:space="preserve">嬉しい…！よろしくお願いします…！頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.emotional[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11225,14 +11225,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ…なんか入ってこない…!?もっとやれるはずなのに</t>
+          <t xml:space="preserve">体が軽い…！今ならなんでもできる気がする…！</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.emotional[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11257,14 +11257,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くぅっ…痛い…！ でも、絶対戻ります…！</t>
+          <t xml:space="preserve">体が重い…！やる気はあるのに、体がついてこない…！</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.emotional[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.emotional[2]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11289,14 +11289,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅ…こんなの悔しい…！</t>
+          <t xml:space="preserve">あれ…なんか入ってこない…！？もっとやれるはずなのに</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.emotional[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.emotional[3]</t>
+          <t xml:space="preserve">injury.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11321,14 +11321,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…！ 絶対に、絶対に戻る…！</t>
+          <t xml:space="preserve">くぅっ…痛い…！ でも、絶対戻ります…！</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.emotional[1]</t>
+          <t xml:space="preserve">injury.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11353,14 +11353,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…ここでの日々、忘れません…！</t>
+          <t xml:space="preserve">うぅ…こんなの悔しい…！</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.emotional[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.emotional[2]</t>
+          <t xml:space="preserve">injury.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11385,14 +11385,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くぅ…ありがとうございました…！ 絶対忘れません…！</t>
+          <t xml:space="preserve">悔しい…！ 絶対に、絶対に戻る…！</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.emotional[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.emotional[3]</t>
+          <t xml:space="preserve">release.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11417,14 +11417,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でも、ありがとう…！ 絶対に戻ってくる…！</t>
+          <t xml:space="preserve">うぅっ…ここでの日々、忘れません…！</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.emotional[1]</t>
+          <t xml:space="preserve">release.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11449,14 +11449,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします…！短い間だけど…全力で…！</t>
+          <t xml:space="preserve">くぅ…ありがとうございました…！ 絶対忘れません…！</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.emotional[1]</t>
+          <t xml:space="preserve">release.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11481,14 +11481,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
+          <t xml:space="preserve">悔しい…でも、ありがとう…！ 絶対に戻ってくる…！</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.emotional[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.emotional[2]</t>
+          <t xml:space="preserve">rentalGreeting.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11513,14 +11513,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰かが見ててくれた…！それだけで、こんなに熱い…！</t>
+          <t xml:space="preserve">よろしくお願いします…！短い間だけど…全力で…！</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.emotional[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11545,14 +11545,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…！悔しい…！でも…絶対諦めない…！</t>
+          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.emotional[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11577,14 +11577,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">守れた…！嬉しい…！次も絶対守る…！</t>
+          <t xml:space="preserve">誰かが見ててくれた…！それだけで、こんなに熱い…！</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.emotional[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11609,14 +11609,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…嘘だよ…ベルトが…！でも…でも諦めない…！</t>
+          <t xml:space="preserve">悔しい…！悔しい…！でも…絶対諦めない…！</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.emotional[1]</t>
+          <t xml:space="preserve">titleDefense.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11641,14 +11641,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわああ…！チャンピオン…！嬉しい…泣いちゃう…！</t>
+          <t xml:space="preserve">守れた…！嬉しい…！次も絶対守る…！</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">titleLoss.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11673,14 +11673,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…ここでの日々、忘れません…！</t>
+          <t xml:space="preserve">嘘…嘘だよ…ベルトが…！でも…でも諦めない…！</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11690,12 +11690,12 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">titleWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11705,14 +11705,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くぅ…ありがとうございました…！ 絶対忘れません…！</t>
+          <t xml:space="preserve">うわああ…！チャンピオン…！嬉しい…泣いちゃう…！</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.emotional[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[3]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11737,14 +11737,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でも、ありがとう…！ 絶対に戻ってくる…！</t>
+          <t xml:space="preserve">うぅっ…ここでの日々、忘れません…！</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11769,14 +11769,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします…！短い間だけど…全力で…！</t>
+          <t xml:space="preserve">くぅ…ありがとうございました…！ 絶対忘れません…！</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11786,12 +11786,12 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11801,14 +11801,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…！悔しい…！でも…絶対諦めない…！</t>
+          <t xml:space="preserve">悔しい…でも、ありがとう…！ 絶対に戻ってくる…！</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="12">
@@ -11833,14 +11833,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">守れた…！嬉しい…！次も絶対守る…！</t>
+          <t xml:space="preserve">よろしくお願いします…！短い間だけど…全力で…！</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="12">
@@ -11865,14 +11865,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…嘘だよ…ベルトが…！でも…でも諦めない…！</t>
+          <t xml:space="preserve">悔しい…！悔しい…！でも…絶対諦めない…！</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="12">
@@ -11897,14 +11897,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわああ…！チャンピオン…！嬉しい…泣いちゃう…！</t>
+          <t xml:space="preserve">守れた…！嬉しい…！次も絶対守る…！</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11914,29 +11914,29 @@
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.emotional.standard[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えると苦しい…もう無理…</t>
+          <t xml:space="preserve">嘘…嘘だよ…ベルトが…！でも…でも諦めない…！</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11946,29 +11946,29 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.standard[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">離れていく…嫌だ…こんなの…</t>
+          <t xml:space="preserve">うわああ…！チャンピオン…！嬉しい…泣いちゃう…！</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.standard[2]</t>
+          <t xml:space="preserve">bond_39_down.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -11993,14 +11993,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして…前みたいに話してくれないの…</t>
+          <t xml:space="preserve">考えると苦しい…もう無理…</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12025,14 +12025,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…考えると胸が温かくなるんです…！</t>
+          <t xml:space="preserve">離れていく…嫌だ…こんなの…</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12057,14 +12057,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると元気が出る…！ 大好き…！</t>
+          <t xml:space="preserve">どうして…前みたいに話してくれないの…</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12089,14 +12089,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人のためなら何でもできる…！ 絶対に守る…！</t>
+          <t xml:space="preserve">…考えると胸が温かくなるんです…！</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12121,14 +12121,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出会えてよかった…本当に…！</t>
+          <t xml:space="preserve">一緒にいると元気が出る…！ 大好き…！</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -12153,14 +12153,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">因縁…終わっちゃったんだ…少し寂しい…</t>
+          <t xml:space="preserve">この人のためなら何でもできる…！ 絶対に守る…！</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -12185,14 +12185,14 @@
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの熱さが消えていく。これでいいのかな…</t>
+          <t xml:space="preserve">出会えてよかった…本当に…！</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12217,14 +12217,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けない…！ 絶対に…！</t>
+          <t xml:space="preserve">因縁…終わっちゃったんだ…少し寂しい…</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12249,14 +12249,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えると胸が熱くなる…！</t>
+          <t xml:space="preserve">……あの熱さが消えていく。これでいいのかな…</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12281,14 +12281,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…考えると熱くなる…！</t>
+          <t xml:space="preserve">絶対に負けない…！ 絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12313,14 +12313,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…超えてみせる…！！</t>
+          <t xml:space="preserve">考えると胸が熱くなる…！</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12345,14 +12345,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この出会いがなければ今の私はなかった…！</t>
+          <t xml:space="preserve">くっ…考えると熱くなる…！</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.standard[2]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12377,14 +12377,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この因縁に終わりなんてない…！ 永遠に戦い続ける…！</t>
+          <t xml:space="preserve">絶対に…超えてみせる…！！</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.standard[1]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12409,14 +12409,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのこと…大好き…！ この団体のために全力を尽くす…！</t>
+          <t xml:space="preserve">この出会いがなければ今の私はなかった…！</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.standard[2]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12441,14 +12441,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで出会えた仲間は宝物…絶対に裏切らない…！</t>
+          <t xml:space="preserve">この因縁に終わりなんてない…！ 永遠に戦い続ける…！</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.standard[1]</t>
+          <t xml:space="preserve">trust_above_75.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12473,14 +12473,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…信じられない…！ どうして…！</t>
+          <t xml:space="preserve">みんなのこと…大好き…！ この団体のために全力を尽くす…！</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.standard[2]</t>
+          <t xml:space="preserve">trust_above_75.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12505,14 +12505,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切られた…全部…嘘だったの…？</t>
+          <t xml:space="preserve">ここで出会えた仲間は宝物…絶対に裏切らない…！</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.emotional.standard[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12537,14 +12537,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不安…こんなんでいいの…？ 私のこと忘れてない…？</t>
+          <t xml:space="preserve">もう…信じられない…！ どうして…！</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.standard[2]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12554,12 +12554,12 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.emotional[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.standard[2]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12569,14 +12569,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…認めたくないけど、あの人は強かった…！</t>
+          <t xml:space="preserve">裏切られた…全部…嘘だったの…？</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.standard[1]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12586,12 +12586,12 @@
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.emotional[2]</t>
+          <t xml:space="preserve">trust_below_35.emotional.standard[1]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12601,14 +12601,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた…でも…この試合は…忘れない…！</t>
+          <t xml:space="preserve">不安…こんなんでいいの…？ 私のこと忘れてない…？</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12633,14 +12633,14 @@
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高…！ 最高の試合だった…！ 泣いちゃう…！</t>
+          <t xml:space="preserve">くっ…認めたくないけど、あの人は強かった…！</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12665,14 +12665,14 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この瞬間のために生きてるんだ…！！</t>
+          <t xml:space="preserve">負けた…でも…この試合は…忘れない…！</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12697,14 +12697,14 @@
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…悔しい…！ 涙が止まらない…</t>
+          <t xml:space="preserve">最高…！ 最高の試合だった…！ 泣いちゃう…！</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12729,14 +12729,14 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた…負けた…もう嫌だ…！</t>
+          <t xml:space="preserve">この瞬間のために生きてるんだ…！！</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12761,14 +12761,14 @@
       </c>
       <c r="F390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった…！ 勝てた…！ 嬉しい…！</t>
+          <t xml:space="preserve">くっ…悔しい…！ 涙が止まらない…</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-01.loss.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12793,14 +12793,14 @@
       </c>
       <c r="F391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った…！ この気持ち、最高…！</t>
+          <t xml:space="preserve">負けた…負けた…もう嫌だ…！</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12825,14 +12825,14 @@
       </c>
       <c r="F392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対強くなる…！ もっともっと…！</t>
+          <t xml:space="preserve">やった…！ 勝てた…！ 嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-01.win.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12857,14 +12857,14 @@
       </c>
       <c r="F393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習は裏切らない…頑張るぞ…！</t>
+          <t xml:space="preserve">勝った…！ この気持ち、最高…！</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-02.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12889,14 +12889,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして…私のこと忘れてるの…？ 悲しい…</t>
+          <t xml:space="preserve">絶対強くなる…！ もっともっと…！</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-02.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12921,14 +12921,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…！ ここで頑張れるって幸せ…！</t>
+          <t xml:space="preserve">練習は裏切らない…頑張るぞ…！</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12953,14 +12953,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大切にしたい…この関係を…！</t>
+          <t xml:space="preserve">どうして…私のこと忘れてるの…？ 悲しい…</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -12985,14 +12985,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対…！ 絶対に…！！</t>
+          <t xml:space="preserve">嬉しい…！ ここで頑張れるって幸せ…！</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-04.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13017,14 +13017,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出たかった…リングに立ちたかった…！</t>
+          <t xml:space="preserve">大切にしたい…この関係を…！</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-05.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13049,14 +13049,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合したい…みんなと一緒に戦いたい…！</t>
+          <t xml:space="preserve">絶対…！ 絶対に…！！</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-06.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13081,14 +13081,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が動かない…悔しい…早く元気になりたい…</t>
+          <t xml:space="preserve">出たかった…リングに立ちたかった…！</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-06.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -13113,14 +13113,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…どうしたらいいの…</t>
+          <t xml:space="preserve">試合したい…みんなと一緒に戦いたい…！</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-07.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -13145,14 +13145,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てない…私なんかもう…うっ…</t>
+          <t xml:space="preserve">体が動かない…悔しい…早く元気になりたい…</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-08.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -13177,14 +13177,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち続けてる…！ この調子で…もっと…！！</t>
+          <t xml:space="preserve">もう…どうしたらいいの…</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-08.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -13209,14 +13209,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなが戦ってるのに…私だけ…悔しい…！</t>
+          <t xml:space="preserve">勝てない…私なんかもう…うっ…</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-09.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13241,14 +13241,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに…早く…戻りたい…！！</t>
+          <t xml:space="preserve">勝ち続けてる…！ この調子で…もっと…！！</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">GL-10.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13273,14 +13273,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わっちゃった…あの最高の時間…でも、泣いてる場合じゃない！</t>
+          <t xml:space="preserve">みんなが戦ってるのに…私だけ…悔しい…！</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13290,12 +13290,12 @@
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">GL-10.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13305,14 +13305,14 @@
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの感覚を…もう一度…必ず取り戻す…！</t>
+          <t xml:space="preserve">リングに…早く…戻りたい…！！</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13322,29 +13322,29 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体中が痛い…! でも、ここで泣くのは終わってからだ…!</t>
+          <t xml:space="preserve">終わっちゃった…あの最高の時間…でも、泣いてる場合じゃない！</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13354,29 +13354,29 @@
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たんだ…! 最後の一戦、絶対に退かねえ…!</t>
+          <t xml:space="preserve">あの感覚を…もう一度…必ず取り戻す…！</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[3]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13401,14 +13401,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た…! 身体は痛いけど、最後まで絶対立ってやる…!</t>
+          <t xml:space="preserve">身体中が痛い…！ でも、ここで泣くのは終わってからだ…！</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[4]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13423,7 +13423,7 @@
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[4]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13433,14 +13433,14 @@
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ…! 繋いでくれた分、私が締める…! 泣くのは後だ…!</t>
+          <t xml:space="preserve">ここまで来たんだ…！ 最後の一戦、絶対に退かない…！</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13465,14 +13465,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来い…! この一戦、絶対に退かねえ…!</t>
+          <t xml:space="preserve">ここまで来た…！ 身体は痛いけど、最後まで絶対立ってやる…！</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[4]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[4]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13497,14 +13497,14 @@
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">心臓がうるさい…! でも、ここで引いたら仲間に顔向けできねえ…!</t>
+          <t xml:space="preserve">あと一つ…！ 繋いでくれた分、私が締める…！ 泣くのは後だ…！</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[3]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13529,14 +13529,14 @@
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来い…! 目の前の一人から、全部倒して繋いでやる…!</t>
+          <t xml:space="preserve">来い…！ この一戦、絶対に退かない…！</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[4]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[4]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13561,14 +13561,14 @@
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まりたくない…! この一戦から、全力でいく…!</t>
+          <t xml:space="preserve">心臓がうるさい…！ でも、ここで引いたら仲間に顔向けできない…！</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.emotional[1]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13593,14 +13593,14 @@
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒した…! はぁ、はぁ…! まだ立ってんだよ…! 次、出てこい…!</t>
+          <t xml:space="preserve">来い…！ 目の前の一人から、全部倒して繋いでやる…！</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[4]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="D417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.emotional[2]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[4]</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13625,14 +13625,14 @@
       </c>
       <c r="F417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってねえ…! 息が上がろうが関係あるか…! 次、早く来い…!</t>
+          <t xml:space="preserve">止まりたくない…！ この一戦から、全力でいく…！</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.emotional[3]</t>
+          <t xml:space="preserve">survivor.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13657,14 +13657,14 @@
       </c>
       <c r="F418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人倒した…! はぁ…まだ立ってる…! 次、来い…! ここは渡さねえ…!</t>
+          <t xml:space="preserve">一人ぶっ倒した…！ はぁ、はぁ…！ まだ、まだ立ってる…！ 次、出てこい…！</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[4]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.emotional[4]</t>
+          <t xml:space="preserve">survivor.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13689,14 +13689,14 @@
       </c>
       <c r="F419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わらない…! この勢いのまま、次も倒す…! 出てこい…!</t>
+          <t xml:space="preserve">まだ終わってない…！ 息が上がっても関係ない…！ 次、早く来い…！</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13706,12 +13706,12 @@
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[1]</t>
+          <t xml:space="preserve">survivor.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13721,14 +13721,14 @@
       </c>
       <c r="F420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったんだよ……！ 私だけじゃない、みんなで最後までリングに立ったんだ……！</t>
+          <t xml:space="preserve">一人倒した…！ はぁ…まだ立ってる…！ 次、来い…！ ここは渡さない…！</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[4]</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="C421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D421" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[2]</t>
+          <t xml:space="preserve">survivor.standard.emotional[4]</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13753,14 +13753,14 @@
       </c>
       <c r="F421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた……！ その想いを背負って、最後まで戦えたの……！</t>
+          <t xml:space="preserve">まだ終わらない…！ この勢いのまま、次も倒す…！ 出てこい…！</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="D422" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[3]</t>
+          <t xml:space="preserve">champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13785,14 +13785,14 @@
       </c>
       <c r="F422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと信じてた……！ この三人なら絶対勝てるって……！ ほんとに勝てたんだよ……！</t>
+          <t xml:space="preserve">三人で勝ったんだよ……！ 私だけじゃない、みんなで最後までリングに立ったんだ……！</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="D423" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.emotional[1]</t>
+          <t xml:space="preserve">champion.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13817,14 +13817,14 @@
       </c>
       <c r="F423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな賞じゃ悔しさは消えない……！ 次は絶対、仲間と一緒に優勝するから……！</t>
+          <t xml:space="preserve">仲間が繋いでくれた……！ その想いを背負って、最後まで戦えたの……！</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="D424" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.emotional[2]</t>
+          <t xml:space="preserve">champion.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
@@ -13849,14 +13849,14 @@
       </c>
       <c r="F424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ そんなのどうでもいい……！ 私は、みんなで勝ちたかったんだよ……！</t>
+          <t xml:space="preserve">ずっと信じてた……！ この三人なら絶対勝てるって……！ ほんとに勝てたんだよ……！</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="D425" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.emotional[3]</t>
+          <t xml:space="preserve">defiant.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="2">
@@ -13881,14 +13881,14 @@
       </c>
       <c r="F425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい……！ 一人だけ褒められても、全然嬉しくない……！ 次は絶対……！</t>
+          <t xml:space="preserve">こんな賞じゃ悔しさは消えない……！ 次は絶対、仲間と一緒に優勝するから……！</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="D426" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.emotional[1]</t>
+          <t xml:space="preserve">defiant.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="2">
@@ -13913,14 +13913,14 @@
       </c>
       <c r="F426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理だって何度も思った……！ でも、みんなの顔が見えたら、倒れられなかった……！</t>
+          <t xml:space="preserve">MVP？ そんなのどうでもいい……！ 私は、みんなで勝ちたかったんだよ……！</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="D427" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.emotional[2]</t>
+          <t xml:space="preserve">defiant.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="2">
@@ -13945,14 +13945,14 @@
       </c>
       <c r="F427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全身が痛い……！ でも嬉しい……！ 最後まで立ってたよ、見ててくれた……！？</t>
+          <t xml:space="preserve">悔しい……！ 一人だけ褒められても、全然嬉しくない……！ 次は絶対……！</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="D428" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.emotional[3]</t>
+          <t xml:space="preserve">gauntlet.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="2">
@@ -13977,14 +13977,14 @@
       </c>
       <c r="F428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても、絶対倒れないって決めたの……！ 約束、守れたよね……！？</t>
+          <t xml:space="preserve">もう無理だって何度も思った……！ でも、みんなの顔が見えたら、倒れられなかった……！</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="C429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D429" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="2">
@@ -14009,14 +14009,14 @@
       </c>
       <c r="F429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…っ！ うそ…本当に…？ 嬉しい…！</t>
+          <t xml:space="preserve">全身が痛い……！ でも嬉しい……！ 最後まで立ってたよ、見ててくれた……！？</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="C430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D430" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[2]</t>
+          <t xml:space="preserve">gauntlet.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="2">
@@ -14041,14 +14041,14 @@
       </c>
       <c r="F430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…涙が止まらない…！ ありがとう…みんな…！</t>
+          <t xml:space="preserve">何人来ても、絶対倒れないって決めたの……！ 約束、守れたよね……！？</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="D431" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.emotional[1]</t>
+          <t xml:space="preserve">champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="2">
@@ -14073,14 +14073,14 @@
       </c>
       <c r="F431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…悔しい…！ でも…絶対に次は…！</t>
+          <t xml:space="preserve">優勝…っ！ うそ…本当に…？ 嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="D432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.emotional[2]</t>
+          <t xml:space="preserve">champion.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="2">
@@ -14105,14 +14105,14 @@
       </c>
       <c r="F432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた…。でも…この悔しさが…力になる…！</t>
+          <t xml:space="preserve">もう…涙が止まらない…！ ありがとう…みんな…！</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.emotional[1]</t>
+          <t xml:space="preserve">postLose.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
@@ -14137,14 +14137,14 @@
       </c>
       <c r="F433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った…！ 嬉しい…！ でもまだ泣かない…！</t>
+          <t xml:space="preserve">くっ…悔しい…！ でも…絶対に次は…！</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.emotional[2]</t>
+          <t xml:space="preserve">postLose.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -14169,14 +14169,14 @@
       </c>
       <c r="F434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この気持ちのまま…次も…！ 絶対負けない…！</t>
+          <t xml:space="preserve">負けた…。でも…この悔しさが…力になる…！</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.emotional[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="2">
@@ -14201,14 +14201,14 @@
       </c>
       <c r="F435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の大会だった…！ この経験、絶対忘れない…！</t>
+          <t xml:space="preserve">勝った…！ 嬉しい…！ でもまだ泣かない…！</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.emotional[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="2">
@@ -14233,14 +14233,14 @@
       </c>
       <c r="F436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戦えてよかった…！ もっともっと強くなる…！</t>
+          <t xml:space="preserve">この気持ちのまま…次も…！ 絶対負けない…！</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
+          <t xml:space="preserve">postWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14265,14 +14265,14 @@
       </c>
       <c r="F437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝…！ 信じられない…でも…勝ちたい…！</t>
+          <t xml:space="preserve">最高の大会だった…！ この経験、絶対忘れない…！</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
+          <t xml:space="preserve">postWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14297,14 +14297,14 @@
       </c>
       <c r="F438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たんだ…泣くのは全部終わってから…！</t>
+          <t xml:space="preserve">戦えてよかった…！ もっともっと強くなる…！</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="2">
@@ -14329,14 +14329,14 @@
       </c>
       <c r="F439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドキドキが止まらない…！ でも…負けたくない…！</t>
+          <t xml:space="preserve">決勝…！ 信じられない…でも…勝ちたい…！</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14361,14 +14361,14 @@
       </c>
       <c r="F440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この熱い気持ちのまま…ぶつかる…！</t>
+          <t xml:space="preserve">ここまで来たんだ…泣くのは全部終わってから…！</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.emotional[1]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14393,14 +14393,14 @@
       </c>
       <c r="F441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった…！ 選ばれた…！ 絶対頑張る…！</t>
+          <t xml:space="preserve">ドキドキが止まらない…！ でも…負けたくない…！</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.emotional[2]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14425,14 +14425,14 @@
       </c>
       <c r="F442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この気持ち…抑えきれない…！ 全力で行くから…！</t>
+          <t xml:space="preserve">この熱い気持ちのまま…ぶつかる…！</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14442,12 +14442,12 @@
       </c>
       <c r="C443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">summon.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="2">
@@ -14457,14 +14457,14 @@
       </c>
       <c r="F443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対…絶対負けない…！全力でいく…！</t>
+          <t xml:space="preserve">やった…！ 選ばれた…！ 絶対頑張る…！</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="C444" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">summon.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E444" t="inlineStr" s="2">
@@ -14489,14 +14489,14 @@
       </c>
       <c r="F444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい……！ 嬉しいよ……！ ここまで来るのに、どれだけ泣いたか……！</t>
+          <t xml:space="preserve">この気持ち…抑えきれない…！ 全力で行くから…！</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14506,12 +14506,12 @@
       </c>
       <c r="C445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="2">
@@ -14521,14 +14521,14 @@
       </c>
       <c r="F445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな……ありがとう……！ 私、やったよ……！（号泣）</t>
+          <t xml:space="preserve">絶対…絶対負けない…！全力でいく…！</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.emotional[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C446" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D446" t="inlineStr" s="12">
@@ -14553,14 +14553,14 @@
       </c>
       <c r="F446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと…あなたたちの団体が気になってたの…！ 勝負して…！</t>
+          <t xml:space="preserve">嬉しい……！ 嬉しいよ……！ ここまで来るのに、どれだけ泣いたか……！</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.emotional[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="C447" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D447" t="inlineStr" s="12">
@@ -14585,14 +14585,14 @@
       </c>
       <c r="F447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この熱い気持ち…ぶつけさせてもらう…！</t>
+          <t xml:space="preserve">みんな……ありがとう……！ 私、やったよ……！（号泣）</t>
         </is>
       </c>
     </row>
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="C448" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D448" t="inlineStr" s="12">
@@ -14617,14 +14617,14 @@
       </c>
       <c r="F448" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるの…？ そんなの…ずるいよ…！</t>
+          <t xml:space="preserve">ずっと…あなたたちの団体が気になってたの…！ 勝負して…！</t>
         </is>
       </c>
     </row>
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="C449" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D449" t="inlineStr" s="12">
@@ -14649,14 +14649,14 @@
       </c>
       <c r="F449" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こっちはこんなに燃えてるのに…！ 受けてよ…！</t>
+          <t xml:space="preserve">この熱い気持ち…ぶつけさせてもらう…！</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="C450" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D450" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E450" t="inlineStr" s="2">
@@ -14681,14 +14681,14 @@
       </c>
       <c r="F450" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…！ こんなの…こんなの嫌だ…！</t>
+          <t xml:space="preserve">逃げるの…？ そんなの…ずるいよ…！</t>
         </is>
       </c>
     </row>
     <row r="451" ht="40" customHeight="1">
       <c r="A451" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="2">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="C451" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D451" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E451" t="inlineStr" s="2">
@@ -14713,14 +14713,14 @@
       </c>
       <c r="F451" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この悔しさ…絶対忘れない…！ 絶対リベンジする…！</t>
+          <t xml:space="preserve">こっちはこんなに燃えてるのに…！ 受けてよ…！</t>
         </is>
       </c>
     </row>
     <row r="452" ht="40" customHeight="1">
       <c r="A452" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B452" t="inlineStr" s="2">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="D452" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.emotional[1]</t>
+          <t xml:space="preserve">result_lose.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E452" t="inlineStr" s="2">
@@ -14745,14 +14745,14 @@
       </c>
       <c r="F452" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った…！ 勝ったよ…！ みんなありがとう…！</t>
+          <t xml:space="preserve">悔しい…！ こんなの…こんなの嫌だ…！</t>
         </is>
       </c>
     </row>
     <row r="453" ht="40" customHeight="1">
       <c r="A453" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="2">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="D453" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.emotional[2]</t>
+          <t xml:space="preserve">result_lose.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E453" t="inlineStr" s="2">
@@ -14777,14 +14777,14 @@
       </c>
       <c r="F453" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この嬉しさ…言葉にならない…！</t>
+          <t xml:space="preserve">この悔しさ…絶対忘れない…！ 絶対リベンジする…！</t>
         </is>
       </c>
     </row>
     <row r="454" ht="40" customHeight="1">
       <c r="A454" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B454" t="inlineStr" s="2">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="C454" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D454" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">result_win.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E454" t="inlineStr" s="2">
@@ -14809,14 +14809,14 @@
       </c>
       <c r="F454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った…勝ったよぉ…！ うちの団体の強さ、見せられたよね…！？</t>
+          <t xml:space="preserve">勝った…！ 勝ったよ…！ みんなありがとう…！</t>
         </is>
       </c>
     </row>
     <row r="455" ht="40" customHeight="1">
       <c r="A455" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B455" t="inlineStr" s="2">
@@ -14826,12 +14826,12 @@
       </c>
       <c r="C455" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D455" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">result_win.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E455" t="inlineStr" s="2">
@@ -14841,14 +14841,14 @@
       </c>
       <c r="F455" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなの期待に…応えられた…よね？ うぅ…よかった…！</t>
+          <t xml:space="preserve">この嬉しさ…言葉にならない…！</t>
         </is>
       </c>
     </row>
     <row r="456" ht="40" customHeight="1">
       <c r="A456" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B456" t="inlineStr" s="2">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="D456" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[3]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E456" t="inlineStr" s="2">
@@ -14873,14 +14873,14 @@
       </c>
       <c r="F456" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…絶対に負けたくなかった…！ 団体のみんなのために…！</t>
+          <t xml:space="preserve">勝った…勝ったよぉ…！ うちの団体の強さ、見せられたよね…！？</t>
         </is>
       </c>
     </row>
     <row r="457" ht="40" customHeight="1">
       <c r="A457" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B457" t="inlineStr" s="2">
@@ -14890,29 +14890,29 @@
       </c>
       <c r="C457" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D457" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E457" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F457" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">涙が止まらない…！こんなに幸せなことがあっていいのかな…！</t>
+          <t xml:space="preserve">みんなの期待に…応えられた…よね？ うぅ…よかった…！</t>
         </is>
       </c>
     </row>
     <row r="458" ht="40" customHeight="1">
       <c r="A458" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B458" t="inlineStr" s="2">
@@ -14922,29 +14922,29 @@
       </c>
       <c r="C458" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D458" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E458" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F458" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなありがとう…！最高だよ…！</t>
+          <t xml:space="preserve">絶対に…絶対に負けたくなかった…！ 団体のみんなのために…！</t>
         </is>
       </c>
     </row>
     <row r="459" ht="40" customHeight="1">
       <c r="A459" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B459" t="inlineStr" s="2">
@@ -14954,29 +14954,29 @@
       </c>
       <c r="C459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D459" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">fighter.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F459" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
+          <t xml:space="preserve">涙が止まらない…！こんなに幸せなことがあっていいのかな…！</t>
         </is>
       </c>
     </row>
     <row r="460" ht="40" customHeight="1">
       <c r="A460" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B460" t="inlineStr" s="2">
@@ -14986,29 +14986,29 @@
       </c>
       <c r="C460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D460" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">fighter.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F460" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれた…！この恩、絶対に返す…！</t>
+          <t xml:space="preserve">みんなありがとう…！最高だよ…！</t>
         </is>
       </c>
     </row>
     <row r="461" ht="40" customHeight="1">
       <c r="A461" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B461" t="inlineStr" s="2">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C461" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D461" t="inlineStr" s="12">
@@ -15033,44 +15033,108 @@
       </c>
       <c r="F461" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
+          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
         </is>
       </c>
     </row>
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">呼んでくれた…！ この恩、絶対に返す…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="40" customHeight="1">
+      <c r="A463" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="40" customHeight="1">
+      <c r="A464" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.emotional[2]</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr" s="2">
+      <c r="B464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr" s="12">
+      <c r="D464" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
-      <c r="E462" t="inlineStr" s="2">
+      <c r="E464" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr" s="3">
+      <c r="F464" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">誰かが見ててくれた…！それだけで、こんなに熱い…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H462"/>
+  <autoFilter ref="A1:H464"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×感情的.xlsx
@@ -257,7 +257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H464"/>
+  <dimension ref="A1:H466"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -12864,7 +12864,7 @@
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12889,14 +12889,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対強くなる…！ もっともっと…！</t>
+          <t xml:space="preserve">悔しい…！あいつの顔を見たくない…！</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12921,14 +12921,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習は裏切らない…頑張るぞ…！</t>
+          <t xml:space="preserve">なんで…なんであいつのことが頭から消えないの…！</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-02.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12953,14 +12953,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして…私のこと忘れてるの…？ 悲しい…</t>
+          <t xml:space="preserve">絶対強くなる…！ もっともっと…！</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-02.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -12985,14 +12985,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…！ ここで頑張れるって幸せ…！</t>
+          <t xml:space="preserve">練習は裏切らない…頑張るぞ…！</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13017,14 +13017,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大切にしたい…この関係を…！</t>
+          <t xml:space="preserve">どうして…私のこと忘れてるの…？ 悲しい…</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13049,14 +13049,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対…！ 絶対に…！！</t>
+          <t xml:space="preserve">嬉しい…！ ここで頑張れるって幸せ…！</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-04.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13081,14 +13081,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出たかった…リングに立ちたかった…！</t>
+          <t xml:space="preserve">大切にしたい…この関係を…！</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-05.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -13113,14 +13113,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合したい…みんなと一緒に戦いたい…！</t>
+          <t xml:space="preserve">絶対…！ 絶対に…！！</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-06.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -13145,14 +13145,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が動かない…悔しい…早く元気になりたい…</t>
+          <t xml:space="preserve">出たかった…リングに立ちたかった…！</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-06.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -13177,14 +13177,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…どうしたらいいの…</t>
+          <t xml:space="preserve">試合したい…みんなと一緒に戦いたい…！</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-07.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -13209,14 +13209,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てない…私なんかもう…うっ…</t>
+          <t xml:space="preserve">体が動かない…悔しい…早く元気になりたい…</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-08.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13241,14 +13241,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち続けてる…！ この調子で…もっと…！！</t>
+          <t xml:space="preserve">もう…どうしたらいいの…</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.emotional[1]</t>
+          <t xml:space="preserve">GL-08.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13273,14 +13273,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなが戦ってるのに…私だけ…悔しい…！</t>
+          <t xml:space="preserve">勝てない…私なんかもう…うっ…</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.emotional[2]</t>
+          <t xml:space="preserve">GL-09.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13305,14 +13305,14 @@
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに…早く…戻りたい…！！</t>
+          <t xml:space="preserve">勝ち続けてる…！ この調子で…もっと…！！</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">GL-10.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13337,14 +13337,14 @@
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わっちゃった…あの最高の時間…でも、泣いてる場合じゃない！</t>
+          <t xml:space="preserve">みんなが戦ってるのに…私だけ…悔しい…！</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13354,12 +13354,12 @@
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">GL-10.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13369,14 +13369,14 @@
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの感覚を…もう一度…必ず取り戻す…！</t>
+          <t xml:space="preserve">リングに…早く…戻りたい…！！</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13386,29 +13386,29 @@
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体中が痛い…！ でも、ここで泣くのは終わってからだ…！</t>
+          <t xml:space="preserve">終わっちゃった…あの最高の時間…でも、泣いてる場合じゃない！</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13418,29 +13418,29 @@
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たんだ…！ 最後の一戦、絶対に退かない…！</t>
+          <t xml:space="preserve">あの感覚を…もう一度…必ず取り戻す…！</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[3]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13465,14 +13465,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た…！ 身体は痛いけど、最後まで絶対立ってやる…！</t>
+          <t xml:space="preserve">身体中が痛い…！ でも、ここで泣くのは終わってからだ…！</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[4]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[4]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13497,14 +13497,14 @@
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ…！ 繋いでくれた分、私が締める…！ 泣くのは後だ…！</t>
+          <t xml:space="preserve">ここまで来たんだ…！ 最後の一戦、絶対に退かない…！</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13529,14 +13529,14 @@
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来い…！ この一戦、絶対に退かない…！</t>
+          <t xml:space="preserve">ここまで来た…！ 身体は痛いけど、最後まで絶対立ってやる…！</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.emotional[4]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[4]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13561,14 +13561,14 @@
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">心臓がうるさい…！ でも、ここで引いたら仲間に顔向けできない…！</t>
+          <t xml:space="preserve">あと一つ…！ 繋いでくれた分、私が締める…！ 泣くのは後だ…！</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[3]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13593,14 +13593,14 @@
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来い…！ 目の前の一人から、全部倒して繋いでやる…！</t>
+          <t xml:space="preserve">来い…！ この一戦、絶対に退かない…！</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[4]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="D417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[4]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13625,14 +13625,14 @@
       </c>
       <c r="F417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まりたくない…！ この一戦から、全力でいく…！</t>
+          <t xml:space="preserve">心臓がうるさい…！ でも、ここで引いたら仲間に顔向けできない…！</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.emotional[1]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13657,14 +13657,14 @@
       </c>
       <c r="F418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒した…！ はぁ、はぁ…！ まだ、まだ立ってる…！ 次、出てこい…！</t>
+          <t xml:space="preserve">来い…！ 目の前の一人から、全部倒して繋いでやる…！</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.emotional[4]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.emotional[2]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[4]</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13689,14 +13689,14 @@
       </c>
       <c r="F419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってない…！ 息が上がっても関係ない…！ 次、早く来い…！</t>
+          <t xml:space="preserve">止まりたくない…！ この一戦から、全力でいく…！</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="D420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.emotional[3]</t>
+          <t xml:space="preserve">survivor.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13721,14 +13721,14 @@
       </c>
       <c r="F420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人倒した…！ はぁ…まだ立ってる…！ 次、来い…！ ここは渡さない…！</t>
+          <t xml:space="preserve">一人ぶっ倒した…！ はぁ、はぁ…！ まだ、まだ立ってる…！ 次、出てこい…！</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[4]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="D421" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.emotional[4]</t>
+          <t xml:space="preserve">survivor.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13753,14 +13753,14 @@
       </c>
       <c r="F421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わらない…！ この勢いのまま、次も倒す…！ 出てこい…！</t>
+          <t xml:space="preserve">まだ終わってない…！ 息が上がっても関係ない…！ 次、早く来い…！</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13770,12 +13770,12 @@
       </c>
       <c r="C422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D422" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[1]</t>
+          <t xml:space="preserve">survivor.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13785,14 +13785,14 @@
       </c>
       <c r="F422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったんだよ……！ 私だけじゃない、みんなで最後までリングに立ったんだ……！</t>
+          <t xml:space="preserve">一人倒した…！ はぁ…まだ立ってる…！ 次、来い…！ ここは渡さない…！</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.emotional[4]</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -13802,12 +13802,12 @@
       </c>
       <c r="C423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D423" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[2]</t>
+          <t xml:space="preserve">survivor.standard.emotional[4]</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13817,14 +13817,14 @@
       </c>
       <c r="F423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた……！ その想いを背負って、最後まで戦えたの……！</t>
+          <t xml:space="preserve">まだ終わらない…！ この勢いのまま、次も倒す…！ 出てこい…！</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="D424" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[3]</t>
+          <t xml:space="preserve">champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
@@ -13849,14 +13849,14 @@
       </c>
       <c r="F424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと信じてた……！ この三人なら絶対勝てるって……！ ほんとに勝てたんだよ……！</t>
+          <t xml:space="preserve">三人で勝ったんだよ……！ 私だけじゃない、みんなで最後までリングに立ったんだ……！</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="D425" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.emotional[1]</t>
+          <t xml:space="preserve">champion.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="2">
@@ -13881,14 +13881,14 @@
       </c>
       <c r="F425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな賞じゃ悔しさは消えない……！ 次は絶対、仲間と一緒に優勝するから……！</t>
+          <t xml:space="preserve">仲間が繋いでくれた……！ その想いを背負って、最後まで戦えたの……！</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="D426" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.emotional[2]</t>
+          <t xml:space="preserve">champion.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="2">
@@ -13913,14 +13913,14 @@
       </c>
       <c r="F426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ そんなのどうでもいい……！ 私は、みんなで勝ちたかったんだよ……！</t>
+          <t xml:space="preserve">ずっと信じてた……！ この三人なら絶対勝てるって……！ ほんとに勝てたんだよ……！</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="D427" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.emotional[3]</t>
+          <t xml:space="preserve">defiant.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="2">
@@ -13945,14 +13945,14 @@
       </c>
       <c r="F427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい……！ 一人だけ褒められても、全然嬉しくない……！ 次は絶対……！</t>
+          <t xml:space="preserve">こんな賞じゃ悔しさは消えない……！ 次は絶対、仲間と一緒に優勝するから……！</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="D428" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.emotional[1]</t>
+          <t xml:space="preserve">defiant.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="2">
@@ -13977,14 +13977,14 @@
       </c>
       <c r="F428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理だって何度も思った……！ でも、みんなの顔が見えたら、倒れられなかった……！</t>
+          <t xml:space="preserve">MVP？ そんなのどうでもいい……！ 私は、みんなで勝ちたかったんだよ……！</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="D429" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.emotional[2]</t>
+          <t xml:space="preserve">defiant.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="2">
@@ -14009,14 +14009,14 @@
       </c>
       <c r="F429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全身が痛い……！ でも嬉しい……！ 最後まで立ってたよ、見ててくれた……！？</t>
+          <t xml:space="preserve">悔しい……！ 一人だけ褒められても、全然嬉しくない……！ 次は絶対……！</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="D430" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.emotional[3]</t>
+          <t xml:space="preserve">gauntlet.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="2">
@@ -14041,14 +14041,14 @@
       </c>
       <c r="F430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても、絶対倒れないって決めたの……！ 約束、守れたよね……！？</t>
+          <t xml:space="preserve">もう無理だって何度も思った……！ でも、みんなの顔が見えたら、倒れられなかった……！</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="C431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D431" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="2">
@@ -14073,14 +14073,14 @@
       </c>
       <c r="F431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…っ！ うそ…本当に…？ 嬉しい…！</t>
+          <t xml:space="preserve">全身が痛い……！ でも嬉しい……！ 最後まで立ってたよ、見ててくれた……！？</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -14090,12 +14090,12 @@
       </c>
       <c r="C432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.emotional[2]</t>
+          <t xml:space="preserve">gauntlet.standard.emotional[3]</t>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="2">
@@ -14105,14 +14105,14 @@
       </c>
       <c r="F432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…涙が止まらない…！ ありがとう…みんな…！</t>
+          <t xml:space="preserve">何人来ても、絶対倒れないって決めたの……！ 約束、守れたよね……！？</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.emotional[1]</t>
+          <t xml:space="preserve">champion.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
@@ -14137,14 +14137,14 @@
       </c>
       <c r="F433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…悔しい…！ でも…絶対に次は…！</t>
+          <t xml:space="preserve">優勝…っ！ うそ…本当に…？ 嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.emotional[2]</t>
+          <t xml:space="preserve">champion.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -14169,14 +14169,14 @@
       </c>
       <c r="F434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた…。でも…この悔しさが…力になる…！</t>
+          <t xml:space="preserve">もう…涙が止まらない…！ ありがとう…みんな…！</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.emotional[1]</t>
+          <t xml:space="preserve">postLose.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="2">
@@ -14201,14 +14201,14 @@
       </c>
       <c r="F435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った…！ 嬉しい…！ でもまだ泣かない…！</t>
+          <t xml:space="preserve">くっ…悔しい…！ でも…絶対に次は…！</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.emotional[2]</t>
+          <t xml:space="preserve">postLose.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="2">
@@ -14233,14 +14233,14 @@
       </c>
       <c r="F436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この気持ちのまま…次も…！ 絶対負けない…！</t>
+          <t xml:space="preserve">負けた…。でも…この悔しさが…力になる…！</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.emotional[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14265,14 +14265,14 @@
       </c>
       <c r="F437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の大会だった…！ この経験、絶対忘れない…！</t>
+          <t xml:space="preserve">勝った…！ 嬉しい…！ でもまだ泣かない…！</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.emotional[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14297,14 +14297,14 @@
       </c>
       <c r="F438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戦えてよかった…！ もっともっと強くなる…！</t>
+          <t xml:space="preserve">この気持ちのまま…次も…！ 絶対負けない…！</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
+          <t xml:space="preserve">postWin.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="2">
@@ -14329,14 +14329,14 @@
       </c>
       <c r="F439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝…！ 信じられない…でも…勝ちたい…！</t>
+          <t xml:space="preserve">最高の大会だった…！ この経験、絶対忘れない…！</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
+          <t xml:space="preserve">postWin.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14361,14 +14361,14 @@
       </c>
       <c r="F440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たんだ…泣くのは全部終わってから…！</t>
+          <t xml:space="preserve">戦えてよかった…！ もっともっと強くなる…！</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14393,14 +14393,14 @@
       </c>
       <c r="F441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドキドキが止まらない…！ でも…負けたくない…！</t>
+          <t xml:space="preserve">決勝…！ 信じられない…でも…勝ちたい…！</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
+          <t xml:space="preserve">preFinal.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14425,14 +14425,14 @@
       </c>
       <c r="F442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この熱い気持ちのまま…ぶつかる…！</t>
+          <t xml:space="preserve">ここまで来たんだ…泣くのは全部終わってから…！</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.emotional[1]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="2">
@@ -14457,14 +14457,14 @@
       </c>
       <c r="F443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった…！ 選ばれた…！ 絶対頑張る…！</t>
+          <t xml:space="preserve">ドキドキが止まらない…！ でも…負けたくない…！</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.emotional[2]</t>
+          <t xml:space="preserve">preMatch.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E444" t="inlineStr" s="2">
@@ -14489,14 +14489,14 @@
       </c>
       <c r="F444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この気持ち…抑えきれない…！ 全力で行くから…！</t>
+          <t xml:space="preserve">この熱い気持ちのまま…ぶつかる…！</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14506,12 +14506,12 @@
       </c>
       <c r="C445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">summon.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="2">
@@ -14521,14 +14521,14 @@
       </c>
       <c r="F445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対…絶対負けない…！全力でいく…！</t>
+          <t xml:space="preserve">やった…！ 選ばれた…！ 絶対頑張る…！</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="C446" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">summon.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E446" t="inlineStr" s="2">
@@ -14553,14 +14553,14 @@
       </c>
       <c r="F446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい……！ 嬉しいよ……！ ここまで来るのに、どれだけ泣いたか……！</t>
+          <t xml:space="preserve">この気持ち…抑えきれない…！ 全力で行くから…！</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="C447" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E447" t="inlineStr" s="2">
@@ -14585,14 +14585,14 @@
       </c>
       <c r="F447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな……ありがとう……！ 私、やったよ……！（号泣）</t>
+          <t xml:space="preserve">絶対…絶対負けない…！全力でいく…！</t>
         </is>
       </c>
     </row>
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.emotional[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="C448" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D448" t="inlineStr" s="12">
@@ -14617,14 +14617,14 @@
       </c>
       <c r="F448" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと…あなたたちの団体が気になってたの…！ 勝負して…！</t>
+          <t xml:space="preserve">嬉しい……！ 嬉しいよ……！ ここまで来るのに、どれだけ泣いたか……！</t>
         </is>
       </c>
     </row>
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.emotional[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="C449" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D449" t="inlineStr" s="12">
@@ -14649,14 +14649,14 @@
       </c>
       <c r="F449" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この熱い気持ち…ぶつけさせてもらう…！</t>
+          <t xml:space="preserve">みんな……ありがとう……！ 私、やったよ……！（号泣）</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="C450" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D450" t="inlineStr" s="12">
@@ -14681,14 +14681,14 @@
       </c>
       <c r="F450" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるの…？ そんなの…ずるいよ…！</t>
+          <t xml:space="preserve">ずっと…あなたたちの団体が気になってたの…！ 勝負して…！</t>
         </is>
       </c>
     </row>
     <row r="451" ht="40" customHeight="1">
       <c r="A451" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="2">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="C451" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D451" t="inlineStr" s="12">
@@ -14713,14 +14713,14 @@
       </c>
       <c r="F451" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こっちはこんなに燃えてるのに…！ 受けてよ…！</t>
+          <t xml:space="preserve">この熱い気持ち…ぶつけさせてもらう…！</t>
         </is>
       </c>
     </row>
     <row r="452" ht="40" customHeight="1">
       <c r="A452" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B452" t="inlineStr" s="2">
@@ -14730,12 +14730,12 @@
       </c>
       <c r="C452" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D452" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E452" t="inlineStr" s="2">
@@ -14745,14 +14745,14 @@
       </c>
       <c r="F452" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…！ こんなの…こんなの嫌だ…！</t>
+          <t xml:space="preserve">逃げるの…？ そんなの…ずるいよ…！</t>
         </is>
       </c>
     </row>
     <row r="453" ht="40" customHeight="1">
       <c r="A453" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="2">
@@ -14762,12 +14762,12 @@
       </c>
       <c r="C453" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D453" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E453" t="inlineStr" s="2">
@@ -14777,14 +14777,14 @@
       </c>
       <c r="F453" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この悔しさ…絶対忘れない…！ 絶対リベンジする…！</t>
+          <t xml:space="preserve">こっちはこんなに燃えてるのに…！ 受けてよ…！</t>
         </is>
       </c>
     </row>
     <row r="454" ht="40" customHeight="1">
       <c r="A454" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B454" t="inlineStr" s="2">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="D454" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.emotional[1]</t>
+          <t xml:space="preserve">result_lose.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E454" t="inlineStr" s="2">
@@ -14809,14 +14809,14 @@
       </c>
       <c r="F454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った…！ 勝ったよ…！ みんなありがとう…！</t>
+          <t xml:space="preserve">悔しい…！ こんなの…こんなの嫌だ…！</t>
         </is>
       </c>
     </row>
     <row r="455" ht="40" customHeight="1">
       <c r="A455" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B455" t="inlineStr" s="2">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="D455" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.emotional[2]</t>
+          <t xml:space="preserve">result_lose.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E455" t="inlineStr" s="2">
@@ -14841,14 +14841,14 @@
       </c>
       <c r="F455" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この嬉しさ…言葉にならない…！</t>
+          <t xml:space="preserve">この悔しさ…絶対忘れない…！ 絶対リベンジする…！</t>
         </is>
       </c>
     </row>
     <row r="456" ht="40" customHeight="1">
       <c r="A456" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B456" t="inlineStr" s="2">
@@ -14858,12 +14858,12 @@
       </c>
       <c r="C456" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D456" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">result_win.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E456" t="inlineStr" s="2">
@@ -14873,14 +14873,14 @@
       </c>
       <c r="F456" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った…勝ったよぉ…！ うちの団体の強さ、見せられたよね…！？</t>
+          <t xml:space="preserve">勝った…！ 勝ったよ…！ みんなありがとう…！</t>
         </is>
       </c>
     </row>
     <row r="457" ht="40" customHeight="1">
       <c r="A457" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B457" t="inlineStr" s="2">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="C457" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D457" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">result_win.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E457" t="inlineStr" s="2">
@@ -14905,14 +14905,14 @@
       </c>
       <c r="F457" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなの期待に…応えられた…よね？ うぅ…よかった…！</t>
+          <t xml:space="preserve">この嬉しさ…言葉にならない…！</t>
         </is>
       </c>
     </row>
     <row r="458" ht="40" customHeight="1">
       <c r="A458" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B458" t="inlineStr" s="2">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="D458" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[3]</t>
+          <t xml:space="preserve">standard.emotional[1]</t>
         </is>
       </c>
       <c r="E458" t="inlineStr" s="2">
@@ -14937,14 +14937,14 @@
       </c>
       <c r="F458" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…絶対に負けたくなかった…！ 団体のみんなのために…！</t>
+          <t xml:space="preserve">勝った…勝ったよぉ…！ うちの団体の強さ、見せられたよね…！？</t>
         </is>
       </c>
     </row>
     <row r="459" ht="40" customHeight="1">
       <c r="A459" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.emotional[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B459" t="inlineStr" s="2">
@@ -14954,29 +14954,29 @@
       </c>
       <c r="C459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D459" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.emotional[1]</t>
+          <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
       <c r="E459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F459" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">涙が止まらない…！こんなに幸せなことがあっていいのかな…！</t>
+          <t xml:space="preserve">みんなの期待に…応えられた…よね？ うぅ…よかった…！</t>
         </is>
       </c>
     </row>
     <row r="460" ht="40" customHeight="1">
       <c r="A460" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.emotional[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.emotional[3]</t>
         </is>
       </c>
       <c r="B460" t="inlineStr" s="2">
@@ -14986,29 +14986,29 @@
       </c>
       <c r="C460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D460" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.emotional[2]</t>
+          <t xml:space="preserve">standard.emotional[3]</t>
         </is>
       </c>
       <c r="E460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F460" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなありがとう…！最高だよ…！</t>
+          <t xml:space="preserve">絶対に…絶対に負けたくなかった…！ 団体のみんなのために…！</t>
         </is>
       </c>
     </row>
     <row r="461" ht="40" customHeight="1">
       <c r="A461" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B461" t="inlineStr" s="2">
@@ -15018,29 +15018,29 @@
       </c>
       <c r="C461" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D461" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[1]</t>
+          <t xml:space="preserve">fighter.standard.emotional[1]</t>
         </is>
       </c>
       <c r="E461" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F461" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
+          <t xml:space="preserve">涙が止まらない…！こんなに幸せなことがあっていいのかな…！</t>
         </is>
       </c>
     </row>
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.emotional[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.emotional[2]</t>
         </is>
       </c>
       <c r="B462" t="inlineStr" s="2">
@@ -15050,29 +15050,29 @@
       </c>
       <c r="C462" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D462" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.emotional[2]</t>
+          <t xml:space="preserve">fighter.standard.emotional[2]</t>
         </is>
       </c>
       <c r="E462" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F462" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">呼んでくれた…！ この恩、絶対に返す…！</t>
+          <t xml:space="preserve">みんなありがとう…！最高だよ…！</t>
         </is>
       </c>
     </row>
     <row r="463" ht="40" customHeight="1">
       <c r="A463" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.emotional[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.emotional[1]</t>
         </is>
       </c>
       <c r="B463" t="inlineStr" s="2">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="C463" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D463" t="inlineStr" s="12">
@@ -15097,44 +15097,108 @@
       </c>
       <c r="F463" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
+          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
         </is>
       </c>
     </row>
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">呼んでくれた…！ この恩、絶対に返す…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="40" customHeight="1">
+      <c r="A465" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="40" customHeight="1">
+      <c r="A466" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.emotional[2]</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr" s="2">
+      <c r="B466" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr" s="12">
+      <c r="D466" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.emotional[2]</t>
         </is>
       </c>
-      <c r="E464" t="inlineStr" s="2">
+      <c r="E466" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr" s="3">
+      <c r="F466" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">誰かが見ててくれた…！それだけで、こんなに熱い…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H464"/>
+  <autoFilter ref="A1:H466"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×感情的.xlsx
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長! あの人とやりたいんです、お願いします!</t>
+          <t xml:space="preserve">社長！ 三人であちらへ行きたいんです、お願いします！</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう我慢できないんです。あの人と、やらせてください。</t>
+          <t xml:space="preserve">もう我慢できないんです。三人で、乗り込ませてください。</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと考えてました。……お願いします、どうしても!</t>
+          <t xml:space="preserve">ずっと考えてました。……三人で行かせてください、どうしても！</t>
         </is>
       </c>
     </row>
